--- a/glossary-changes/Glossaire CareSets V1 - revised 20260829.xlsx
+++ b/glossary-changes/Glossaire CareSets V1 - revised 20260829.xlsx
@@ -5776,7 +5776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K120"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="29.25" customHeight="1"/>
   <cols>
     <col width="18.5703125" customWidth="1" min="1" max="2"/>
@@ -5786,7 +5786,8 @@
     <col width="15.7109375" customWidth="1" style="3" min="6" max="6"/>
     <col width="88" customWidth="1" style="40" min="7" max="7"/>
     <col width="107.7109375" customWidth="1" style="1" min="8" max="10"/>
-    <col width="16.85546875" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customFormat="1" customHeight="1" s="2">
@@ -5840,7 +5841,17 @@
           <t>Description NL</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Definition EN</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Description EN</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>DataType</t>
         </is>
@@ -5883,6 +5894,16 @@
           <t>Indien de data onbekend zijn, kan ook een levensfase worden vermeld (tijdens de kindertijd, in de adolescentie…)</t>
         </is>
       </c>
+      <c r="K2" s="48" t="inlineStr">
+        <is>
+          <t>date on which a product or vaccine is administered to the patient by the Performer</t>
+        </is>
+      </c>
+      <c r="L2" s="48" t="inlineStr">
+        <is>
+          <t>For vaccines, a life period may also be recorded when the exact date is unknown (during childhood, adolescence, …).</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="105" customHeight="1">
       <c r="B3" s="45" t="inlineStr">
@@ -5923,6 +5944,16 @@
 Wanneer het echter om een familielid of naaste gaat, wordt alleen de rol ingevoerd (bijv.: vader, moeder, buur, mantelzorger, vriend, …) om te voldoen aan de AVG-vereisten. In eerste instantie zal de tekst worden gebruikt die is geïnspireerd op de toekomstige ValueSet en daarna zal de ValueSet ‘VS_PatientRelationshipType’ worden gebruikt, die momenteel wordt gevalideerd bij SNOMED/FHIR International. Dit wordt een transversale ValueSet (bijv. ook gebruikt voor de familiegeschiedenis). Let op: momenteel is er geen verwijzing naar een administratieve CareSet."</t>
         </is>
       </c>
+      <c r="K3" s="48" t="inlineStr">
+        <is>
+          <t>person who reports the information recorded in the CareSet</t>
+        </is>
+      </c>
+      <c r="L3" s="48" t="inlineStr">
+        <is>
+          <t>For example: the patient, the general practitioner, a relative, or the professional recording the information themselves.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="75" customHeight="1">
       <c r="B4" s="45" t="inlineStr">
@@ -5966,7 +5997,12 @@
           <t>Wanneer het echter om een ouder of naaste gaat, wordt alleen de rol ingevoerd (bijv.: vader, moeder, buur, mantelzorger, vriend, …) om te voldoen aan de AVG-vereisten. In eerste instantie zal de tekst worden gebruikt die is geïnspireerd op de toekomstige ValueSet en daarna zal de ValueSet „VS_PatientRelationshipType“ worden gebruikt, die momenteel wordt gevalideerd bij SNOMED/FHIR International. Dit wordt een transversale ValueSet (bijv. ook gebruikt voor de familiegeschiedenis). Let op: momenteel is er geen verwijzing naar een administratieve CareSet.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="48" t="inlineStr">
+        <is>
+          <t>healthcare professional who records the content of the CareSet and takes responsibility for it</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Ref/niss/??</t>
         </is>
@@ -6009,6 +6045,16 @@
           <t>Links,rechts,beiden</t>
         </is>
       </c>
+      <c r="K5" s="48" t="inlineStr">
+        <is>
+          <t>side of the body to which the recorded information refers</t>
+        </is>
+      </c>
+      <c r="L5" s="48" t="inlineStr">
+        <is>
+          <t>Right, left, or both.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="B6" s="45" t="inlineStr">
@@ -6052,6 +6098,16 @@
           <t xml:space="preserve"> (hoofd, been, dijbeen, hart, …)</t>
         </is>
       </c>
+      <c r="K6" s="48" t="inlineStr">
+        <is>
+          <t>part of the body to which the recorded information refers</t>
+        </is>
+      </c>
+      <c r="L6" s="48" t="inlineStr">
+        <is>
+          <t>For example: head, leg, femur, heart, …</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="45" t="inlineStr">
@@ -6090,6 +6146,16 @@
           <t>zoals bovenste/onderste, mediaal/lateraal of inwendig/uitwendig.</t>
         </is>
       </c>
+      <c r="K7" s="48" t="inlineStr">
+        <is>
+          <t>relative position, within the body part concerned, of the site to which the recorded information refers</t>
+        </is>
+      </c>
+      <c r="L7" s="48" t="inlineStr">
+        <is>
+          <t>For example: superior/inferior, medial/lateral, internal/external.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="B8" s="45" t="inlineStr">
@@ -6135,6 +6201,11 @@
           <t>Normaal gesproken is slechts één identificatiecode toegestaan, maar in bepaalde gevallen zijn meerdere identificatiecodes toegestaan (bijv.: paspoortnummer, NISS-nummer in het Bepatient-systeem, Belrai-ID)</t>
         </is>
       </c>
+      <c r="K8" s="48" t="inlineStr">
+        <is>
+          <t>identifier that designates a CareSet instance and is unique within the namespace of the system that assigns it</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="49.5" customHeight="1">
       <c r="B9" s="45" t="inlineStr">
@@ -6171,6 +6242,11 @@
         </is>
       </c>
       <c r="J9" s="1" t="n"/>
+      <c r="K9" s="48" t="inlineStr">
+        <is>
+          <t>attribute classifying a data element by its clinical or functional meaning, allowing its occurrences to be grouped</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="45" t="inlineStr">
@@ -6204,6 +6280,16 @@
           <t>toestand die de klinische actualiteit van de geregistreerde informatie weergeeft</t>
         </is>
       </c>
+      <c r="K10" s="48" t="inlineStr">
+        <is>
+          <t>state expressing the clinical currency of the recorded information</t>
+        </is>
+      </c>
+      <c r="L10" s="48" t="inlineStr">
+        <is>
+          <t>For example: active, inactive, resolved, entered-in-error.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="B11" s="45" t="inlineStr">
@@ -6232,6 +6318,11 @@
           <t>gecodeerde waarde die het klinische concept aanduidt waarop de geregistreerde informatie betrekking heeft</t>
         </is>
       </c>
+      <c r="K11" s="48" t="inlineStr">
+        <is>
+          <t>coded value designating the clinical concept to which the recorded information refers</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="90" customHeight="1">
       <c r="B12" s="45" t="inlineStr">
@@ -6254,6 +6345,11 @@
           <t>instrument, toestel, apparaat, software of ander artikel dat door de fabrikant bestemd is om bij de mens voor medische doeleinden te worden gebruikt</t>
         </is>
       </c>
+      <c r="K12" s="48" t="inlineStr">
+        <is>
+          <t>instrument, apparatus, appliance, software or other article intended by its manufacturer to be used for medical purposes in human beings</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="B13" s="45" t="inlineStr">
@@ -6295,6 +6391,11 @@
           <t>bijv. kalibratie, vervanging van de batterij, aanpassing van een prothese, aansluiting van een VAC-systeem voor wondverzorging, enz.), en dat een centraal onderdeel van de procedure vormt. De koppeling vindt plaats via een verwijzing naar een Device-bron.</t>
         </is>
       </c>
+      <c r="K13" s="48" t="inlineStr">
+        <is>
+          <t>device intended to be introduced wholly or partly into the human body and to remain there after the procedure</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="45" t="inlineStr">
@@ -6328,6 +6429,11 @@
           <t>identificatie die de fabrikant toekent aan alle eenheden die in eenzelfde productiecyclus zijn vervaardigd</t>
         </is>
       </c>
+      <c r="K14" s="48" t="inlineStr">
+        <is>
+          <t>identifier assigned by the manufacturer to all units produced in the same manufacturing cycle</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="45" t="inlineStr">
@@ -6363,6 +6469,11 @@
           <t>aanvullende informatie over de inhoud van de CareSet, uitgedrukt in vrije tekst</t>
         </is>
       </c>
+      <c r="K15" s="48" t="inlineStr">
+        <is>
+          <t>Additional information related to the CareSet content in free text format</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="45" t="inlineStr">
@@ -6395,6 +6506,11 @@
           <t>Bijvoorbeeld: een MRI-scan op basis van een beeldvormingsvoorschrift, het verstrekken van een geneesmiddel op basis van een medicijnvoorschrift</t>
         </is>
       </c>
+      <c r="K16" s="48" t="inlineStr">
+        <is>
+          <t>request for care or service whose execution is recorded by the CareSet</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="B17" s="45" t="inlineStr">
@@ -6427,6 +6543,16 @@
           <t>Bijvoorbeeld: een biopsie die deel uitmaakt van een chirurgische ingreep</t>
         </is>
       </c>
+      <c r="K17" s="48" t="inlineStr">
+        <is>
+          <t>encompassing CareSet of which the current record forms a component</t>
+        </is>
+      </c>
+      <c r="L17" s="48" t="inlineStr">
+        <is>
+          <t>For example: a biopsy that is part of a surgical intervention.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="B18" s="45" t="inlineStr">
@@ -6465,6 +6591,11 @@
           <t>De patiënt wordt aangeduid met een uniek identificatienummer, dat het nationale registratienummer van de patiënt (NISS) moet zijn. In bepaalde gevallen kan echter een ander uniek identificatienummer worden toegestaan (zoals het BISS-nummer of een combinatie van de achternaam, voornaam(en) en geboortedatum).</t>
         </is>
       </c>
+      <c r="K18" s="48" t="inlineStr">
+        <is>
+          <t>The person who is the subject of the healthcare to which the record (CareSet) refers</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="45" t="inlineStr">
@@ -6503,6 +6634,16 @@
           <t>De unieke identificatiecode moet het nationale registratienummer van de beroepsbeoefenaar (NISS) zijn, of het BIS-nummer indien het NISS of het BIS-nummer bestaat. Indien dit niet het geval is, is het toegestaan om eventueel andere gegevens in te voeren waarmee de beroepsbeoefenaar kan worden geïdentificeerd. Bijvoorbeeld: RIZIV-nummer, voor- en achternaam, identificatienummer voor buitenlandse dienstverleners…</t>
         </is>
       </c>
+      <c r="K19" s="48" t="inlineStr">
+        <is>
+          <t>person who performed the act recorded by the CareSet</t>
+        </is>
+      </c>
+      <c r="L19" s="48" t="inlineStr">
+        <is>
+          <t>For example: administered the vaccine, performed the observation.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="45" t="inlineStr">
@@ -6541,7 +6682,17 @@
           <t xml:space="preserve"> (datum van de laatste update). Maakt het mogelijk om de historiek van de CareSet te beheren via het paar Business Identifier - RecordedDate. Dit zorgt ervoor dat de laatste versie van de inhoud toegankelijk is.</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="48" t="inlineStr">
+        <is>
+          <t>date on which the record was entered by the Recorder</t>
+        </is>
+      </c>
+      <c r="L20" s="48" t="inlineStr">
+        <is>
+          <t>Date of last update. Enables CareSet history management through the Business Identifier / RecordedDate pair, which ensures access to the latest version of the content.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>???</t>
         </is>
@@ -6584,6 +6735,16 @@
           <t>Zie ValueSet VS_Route</t>
         </is>
       </c>
+      <c r="K21" s="48" t="inlineStr">
+        <is>
+          <t>path by which a product is brought into contact with the body</t>
+        </is>
+      </c>
+      <c r="L21" s="48" t="inlineStr">
+        <is>
+          <t>See ValueSet VS_Route.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="45" t="inlineStr">
@@ -6622,6 +6783,11 @@
           <t>(alleen voor één apparaat)</t>
         </is>
       </c>
+      <c r="K22" s="48" t="inlineStr">
+        <is>
+          <t>identifier assigned by the manufacturer to one individual device</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="B23" s="45" t="inlineStr">
@@ -6660,6 +6826,16 @@
           <t>Ex : Final, Corrected, Canceled, Entered_in_err</t>
         </is>
       </c>
+      <c r="K23" s="48" t="inlineStr">
+        <is>
+          <t>state of the record within its lifecycle</t>
+        </is>
+      </c>
+      <c r="L23" s="48" t="inlineStr">
+        <is>
+          <t>For example: final, corrected, cancelled, entered-in-error.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="90" customHeight="1">
       <c r="B24" s="45" t="inlineStr">
@@ -6699,6 +6875,11 @@
       <c r="J24" s="1" t="inlineStr">
         <is>
           <t>(chirurgische robot, bewakingsapparaat, …).</t>
+        </is>
+      </c>
+      <c r="K24" s="48" t="inlineStr">
+        <is>
+          <t>medical device used to carry out the recorded act</t>
         </is>
       </c>
     </row>
@@ -6750,6 +6931,16 @@
  271649006: Systolische bloeddruk
  271650006: Diastolische bloeddruk Code van de component van de CareSet Observatie.
 Deze component wordt uitsluitend gebruikt voor bloeddrukmetingen in het kader van de CareSet ClinicalObservation:"</t>
+        </is>
+      </c>
+      <c r="K25" s="48" t="inlineStr">
+        <is>
+          <t>degree of confirmation assigned to the recorded information</t>
+        </is>
+      </c>
+      <c r="L25" s="48" t="inlineStr">
+        <is>
+          <t>For example: confirmed, unconfirmed, refuted, entered-in-error.</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7346,7 @@
           <t>NoteContext</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Numérique</t>
         </is>
@@ -7190,7 +7381,7 @@
 DiseaseCourse</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Numérique</t>
         </is>
@@ -7768,7 +7959,7 @@
           <t>Addresses</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Ref/niss/??</t>
         </is>
@@ -7831,7 +8022,7 @@
 De préférence, on utilisera d’abord le CTI-Extended è CNK è ATC. Le CTI-Extended a l’avantage de représenter tous les produits médicamenteux commercialisés en Belgique et reconnus par l’agence des médicaments. Le CNK n’est pas toujours présent. Comme cet élément n’est pas obligatoire, dans le cas d’un vaccin étranger, le produit ne sera pas nécessairement mentionné.</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>référence</t>
         </is>
@@ -8012,7 +8203,7 @@
       <c r="H70" s="1" t="n"/>
       <c r="I70" s="1" t="n"/>
       <c r="J70" s="1" t="n"/>
-      <c r="K70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>ValueSet</t>
         </is>
@@ -8227,7 +8418,7 @@
           <t>Severity</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>référence</t>
         </is>
@@ -8428,7 +8619,7 @@
     </row>
     <row r="85" ht="29.25" customHeight="1"/>
     <row r="86">
-      <c r="K86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -8450,7 +8641,7 @@
     <row r="96" ht="29.25" customHeight="1"/>
     <row r="97" ht="29.25" customHeight="1"/>
     <row r="98" ht="29.25" customHeight="1">
-      <c r="K98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
@@ -8466,7 +8657,7 @@
     <row r="106" ht="29.25" customHeight="1"/>
     <row r="107" ht="29.25" customHeight="1"/>
     <row r="108" ht="29.25" customHeight="1">
-      <c r="K108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t>numérique</t>
         </is>
@@ -8485,7 +8676,7 @@
           <t>Problem</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t>numérique ou freetext?</t>
         </is>
